--- a/Data_Baja_Konstruksi_2026-09-15.xlsx
+++ b/Data_Baja_Konstruksi_2026-09-15.xlsx
@@ -473,12 +473,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PT.Baja Sarana Multi</t>
+          <t>PT.Baja Semesta Niaga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0813-6255-5811</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,11 +488,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RWQR+5PQ, Jl. Komp. PT. Wira, RW.6, Cakung Tim., Kec. Cakung, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13910, Indonesia</t>
+          <t>Jl. Cakung Cilincing Raya No.KM.1,5, RT.3/RW.8, Cakung Bar., Kec. Cakung, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13910, Indonesia</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5160687003428264965&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=2847701042583033587&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PT. Jaya Baja Utama - Supplier Pipa Besi Flange Fitting dan Plat</t>
+          <t>PT.KARISA BAJA distributor besi dan baja</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0858-9999-3385</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,20 +528,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jl. Tanah Abang I No.11F 11, RT.14/RW.8, Petojo Sel., Kecamatan Gambir, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10160, Indonesia</t>
+          <t>VR7G+JJ9, Jl. Mangga Dua Raya, RT.11/RW.5, Ancol, Kec. Pademangan, Jkt Utara, Daerah Khusus Ibukota Jakarta 14430, Indonesia</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>http://duniapipa.co.id/</t>
+          <t>http://pt-karisa-baja.blogspot.co.id/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=15280180653279722004&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12615606845706110934&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PT. Pangeran Jayakarta Baja Sakti</t>
+          <t>PT Bangun Bejana Baja</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0812-9387-8995</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jl. Daan Mogot No.3B, RT.6/RW.5, Duri Kepa, Kec. Kb. Jeruk, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11460, Indonesia</t>
+          <t>Jl. Jenderal Ahmad Yani No.17, RT.7/RW.7, Utan Kayu Sel., Kec. Matraman, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13110, Indonesia</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.pangeranjayakartabajasakti.com/</t>
+          <t>http://www.bangunbejanabaja.com/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11865481298274536336&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8736150707297397631&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PT Primari Inrahm Utama - Fabrikator Baja Infrastruktur</t>
+          <t>Pekerjaan Konstruksi Baja</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0899-9774-461</t>
+          <t>0882-8920-0999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,20 +608,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MTH Square Ground Floor (GF) A4 A Jl. Letjen M.T. Haryono Kav 10, RT/RW. 006/012, RW.6, Bidara Cina, Kecamatan Jatinegara, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13330, Indonesia</t>
+          <t>Jakarta, RT.2/RW.12, Kapuk, Kecamatan Cengkareng, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11720, Indonesia</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://primariutama.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=9261309479163477138&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=1520139967036345531&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -633,12 +633,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PT. Solusi Baja Indonesia</t>
+          <t>PT KONSTRUKSIBAJA INDONESIA BERSATU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(021) 54233414</t>
+          <t>(021) 22805214</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -648,20 +648,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Vida Office Building, Jl. Perjuangan No.8 Lt 7, RT.1/RW.7, Kb. Jeruk, Kec. Kb. Jeruk, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11530, Indonesia</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
+          <t>Signature Park Grande, Jl. Letjen M.T. Haryono No.Kav. 20, RT.4/RW.1, Cawang, Kec. Kramat jati, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13630, Indonesia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tidak ada rating</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>http://www.solusibaja.co.id/</t>
+          <t>https://konstruksi-baja.co.id/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8751031934651017034&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9530452783182142443&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -673,12 +675,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PT. Cahaya Benteng Mas</t>
+          <t>Baja Mulia Perkasa PD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(021) 6281964</t>
+          <t>0811-9317-393</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -688,20 +690,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jl. Pangeran Jayakarta No.151, RT.9/RW.10, Mangga Dua Sel., Kecamatan Sawah Besar, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>JL. Kapuk Poglar, 23-24, Jakarta, 11720, RT.13/RW.1, Kapuk, Kecamatan Cengkareng, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11720, Indonesia</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://www.cahayabentengmas.co.id/</t>
+          <t>http://bajamuliaperkasa.id/about-us/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=12873332545475368537&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7035688291406480253&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -713,12 +715,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PT. JAGAT BAJA PRIMA UTAMA (OFFICE)</t>
+          <t>Baja Ringan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(021) 56969178</t>
+          <t>0812-9872-1528</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -728,7 +730,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jl. Tomang Raya No.28 5, RT.5/RW.1, Jatipulo, Kec. Palmerah, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11430, Indonesia</t>
+          <t>FR54+MQV, Gg. Al-Hidayah, RT.02/RW.08, Pasir Jambu, Kec. Sukaraja, Kabupaten Bogor, Jawa Barat 16158, Indonesia</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -736,12 +738,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.jagatbaja.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=18362597872904299293&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=16941594551248174624&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -753,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gorong gorong baja</t>
+          <t>Baja ringan bogor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(021) 82492111</t>
+          <t>0857-9464-2905</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -768,20 +770,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jl. Raya Narogong KM 15, Gg. PP - Pangk 6 No.111, RT.003/RW.004, Ciketing Udik, Kec. Bantar Gebang, Kota Bks, Jawa Barat 17153, Indonesia</t>
+          <t>CRQ2+6WV, Jl. Sholeh Iskandar, RT.01/RW.07, Kedungbadak, Tanah Sareal, Kota Bogor, Jawa Barat 16164, Indonesia</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://pt-cmp.com/</t>
+          <t>https://free.facebook.com/moehamad.moehamad.12?ref_component=mfreebasic_home_header&amp;ref_page=/wap/home.php&amp;refid=8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5315148687822219512&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=14988619866938837642&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -793,12 +795,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PT PANGERAN JAYAKARTA BAJA</t>
+          <t>Focus Cipta Kreasi Bogor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0812-1285-7112</t>
+          <t>(0251) 2020312</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -808,20 +810,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VRF4+332, Jl. Mitra Bahari, RT.9/RW.1, Pluit, Kecamatan Penjaringan, Jkt Utara, Daerah Khusus Ibukota Jakarta 14440, Indonesia</t>
+          <t>Jl. Bogor Nirwana Residence Ruko Orchard, RT.06/RW.12, Mulyaharja, Kec. Bogor Sel., Kota Bogor, Jawa Barat 16135, Indonesia</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>http://www.pangeranjayakartabaja.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8363162590401529067&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11287860686486641215&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -833,12 +835,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MEGA BAJA JAKARTA</t>
+          <t>Java kontruksi bogor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0831-3111-1550</t>
+          <t>0813-8036-7277</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -848,11 +850,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dekat Jl. Sukabumi.2 2, RT.2/RW.7, Menteng, Kec. Menteng, Kota Jakarta Pusat, RT.2/RW.7, Menteng, Kec. Menteng, Jakarta, Daerah Khusus Ibukota Jakarta 10310, Indonesia</t>
+          <t>kp Jl. Raya Cijulang No.04, RT.05, Cadas Ngampar, Kec. Sukaraja, Kabupaten Bogor, Jawa Barat 16710, Indonesia</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -861,7 +863,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8210102105049639643&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=10542889314095264095&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -873,12 +875,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PT Cakung Prima Steel</t>
+          <t>SALES REPRESENTATIF CONWOOD BOGOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(021) 6490666</t>
+          <t>0858-7147-8505</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -888,20 +890,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jl. Pangeran Jayakarta No.117 Blk A1-A2, RT.5/RW.7, Mangga Dua Sel., Kecamatan Sawah Besar, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>CR98+8XF, Jl. Bangbarung Raya, RT.01/RW.11, Bantarjati, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16152, Indonesia</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>http://www.cakungprimasteel.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16858395238072614199&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17708875026113713665&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -913,12 +915,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gerai Baja Indonesia</t>
+          <t>Desain Interior Bogor, Arsitektur, Office Fit Out, Kantor, Renovasi, Apartement, Cafe, Hotel, Restoran, Interior Design ABDI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(021) 29491944</t>
+          <t>0813-1660-8709</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -928,20 +930,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gedung Office 8, Jl. Scbd Lantai 18 A, RT.7/RW.1, Senayan, Kec. Kby. Baru, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12190, Indonesia</t>
+          <t>Komplek Kehutanan Selakopi No D36, RT.03/RW.06, Pasirmulya, Kec. Bogor Bar., Bogor-CDV, Jawa Barat 16118, Indonesia</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>http://www.geraibaja.co.id/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5409796081468582464&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8050651150083357167&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -953,12 +955,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spindo Jakarta (PT.Steel Pipe Industry of Indonesia)</t>
+          <t>Amanah BNR Official | Kontraktor Bangunan Bogor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(021) 62313502</t>
+          <t>0858-1428-9119</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -968,20 +970,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gedung Baja, Jl. Pangeran Jayakarta Dalam No.55 Lt.7, RT.1/RW.9, Mangga Dua Sel., Kecamatan Sawah Besar, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>Jl. Cibeureum Sunting, RT.01/RW.08, Mulyaharja, Kec. Bogor Sel., Kota Bogor, Jawa Barat 16135, Indonesia</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>http://www.spindo.com/</t>
+          <t>https://kontraktorbangunanbogor.com/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=12859984723802559319&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=16513591326197657743&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -993,12 +995,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JUAL BESI BETON COIL PLATE BESI DISTRIBUTOR BAJA</t>
+          <t>VIDEOTRON BOGOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0813-1906-7520</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1008,7 +1010,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pusat, Jl. Pangeran Jayakarta No.55, RT.7/RW.7, Mangga Dua Sel., Kecamatan Sawah Besar, Jakarta, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>Jl. Raya Jakarta-Bogor No.Utara No.95, RT.06/RW.02, 96CibuluhBogor, Cibuluh, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16151, Indonesia</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1016,12 +1018,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>http://saranasteel.co.id/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=12433593529140876158&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9398599083742427267&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1033,12 +1035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CV PANGERAN BAJA SAKTI</t>
+          <t>PT. RIDWAN MAULANA BAJA INDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0812-9566-6538</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1048,20 +1050,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Soho Capital Podomoro City, Jl. Tanjung Duren Raya No.1, RT.3/RW.5, Tj. Duren Sel., Kec. Grogol petamburan, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11470, Indonesia</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
+          <t>Jl. Raya Bogor KM.31 No.9, Cisalak Ps., Kec. Cimanggis, Kota Depok, Jawa Barat 16452, Indonesia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tidak ada rating</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ptpangeranjayakabajasakti.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13938965193463124782&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=16244159203426407375&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1073,12 +1077,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PT. Baja Mandiri Sejahtra Jaya</t>
+          <t>Baja Ringan dan pagar tralis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(021) 6241737</t>
+          <t>0878-4247-2144</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1088,11 +1092,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jl. Pangeran Jayakarta No.139 7, RT.7/RW.7, Mangga Dua Sel., Kecamatan Sawah Besar, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>Jl. Baru Plenongan, Depok, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16435, Indonesia</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7489939551841801997&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=3495134261671320359&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1113,12 +1117,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TOKO BAJA INDO PRIMA</t>
+          <t>Tukang Atap Baja Ringan - Jasa pasang Plafon Gypsum - Pembuatan Kanopi Depok</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0813-3263-0614</t>
+          <t>0821-2388-5400</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1128,11 +1132,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jl. Angkasa No.Kav B-6, RW.10, Gn. Sahari Sel., Kemayoran, Kota, Blk. A3 No.7 Lt GF, RW.10, Gn. Sahari Sel., Jakarta, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10610, Indonesia</t>
+          <t>Jl. H. Muin, Gg. Belimbing 2 Jl. Klp. Dua Raya No.19, Tugu, Kec. Cimanggis, Kota Depok, Jawa Barat 16451, Indonesia</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7380358995205260020&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17949787578147733783&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1153,12 +1157,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bengkel besi konstruksi baja bikin pasang atap rafter wf spandek jembatan lima</t>
+          <t>Material baja ringan ,Bondek , spandek , hollo plafond , besi beton , cakar ayam ,gypsum dll</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0811-9788-108</t>
+          <t>0895-2923-5062</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1168,20 +1172,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jl. KH.Moh.Mansyur No.127 4, RT.4/RW.12, Tanah Sereal, Kec. Tambora, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11270, Indonesia</t>
+          <t>Jl. Sentosa I No.13, Sukamaju, Kec. Cilodong, Kota Depok, Jawa Barat 16475, Indonesia</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bengkelbesibajakonstruksi88</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10262504283442732492&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7577848252899108306&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1193,12 +1197,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TOTAL BAJA JAYA</t>
+          <t>Pitara Baja</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0878-8771-0101</t>
+          <t>0877-7714-6999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1208,20 +1212,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jl. Buni No.4A, RT.3/RW.6, Mangga Besar, Kec. Taman Sari, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11180, Indonesia</t>
+          <t>Jl. Pitara No.145, Pancoran Mas, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16436, Indonesia</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://shopee.co.id/pitarabaja</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5995990311542930391&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=1567164413355414899&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1233,12 +1237,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PT. Hamasa Steel Center</t>
+          <t>Konstruksi Baja Ringan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(021) 6006113</t>
+          <t>0857-1969-2075</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1248,20 +1252,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Jl. Pangeran Jayakarta No.30-A, RT.8/RW.7, Mangga Dua Sel., Kecamatan Sawah Besar, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10730, Indonesia</t>
+          <t>HRXF+M46, Depok, Cimanggis, Depok City, West Java 16431, Indonesia</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://harapanmasa.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10746585701939278281&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=15258991056800495671&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1273,12 +1277,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Konstruksi baja</t>
+          <t>Matahari Kanopi "Jasa Pasang Kanopi Baja Ringan Murah Depok"</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0822-9806-6169</t>
+          <t>0813-8586-5487</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1288,20 +1292,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jl. Kalideres Permai No.25 6, RT.6/RW.14, Kalideres, Kec. Kalideres, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11840, Indonesia</t>
+          <t>Jalan Kemang II, Seberang SMA Negeri 11, Patokannya Musholla Ar-Rohman, Cikumpa Gg. Usen Oton No.68, RT.04/RW.09, Sukmajaya, Kec. Sukmajaya, Kota Depok, Jawa Barat 16412, Indonesia</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.mataharikanopi.com/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2291157847084856649&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7573240433443860647&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1313,12 +1317,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CV. Abdi Remaja Contractor (Jasa Konstruksi Baja)</t>
+          <t>Hi Steel CIBUBUR-pusat penjualan besi beton,baja ringan,wf,H beam,plat acer,plat kapal ( MREK TASO,KS CILEGON)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0859-5902-0918</t>
+          <t>0813-8111-8001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1328,20 +1332,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jl. Peta Utara No.51 B, RT.1/RW.12, Pegadungan, Kec. Kalideres, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11830, Indonesia</t>
+          <t>Jl. Alternatif Cibubur No.Km.7, RT.03/RW.04, Cileungsi, Kec. Cileungsi, Kabupaten Bogor, Jawa Barat 16820, Indonesia</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://www.abdiremajacontractor.com/</t>
+          <t>https://histeel.co.id/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16931631120380786690&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=2146714756948329308&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1353,12 +1357,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KONSTRUKSI BAJA</t>
+          <t>Agen baja ringan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0813-2257-1116</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1368,7 +1372,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jl. Pramuka Sari I No.6 12, RT.6/RW.9, Rawasari, Kec. Cemp. Putih, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10570, Indonesia</t>
+          <t>Jl. H. Nadih No.58-47, Sukamaju, Kec. Cilodong, Kota Depok, Jawa Barat 16415, Indonesia</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5957112857886639238&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7205650335577317953&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1393,12 +1397,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jasa konstruksi baja</t>
+          <t>Hi Steel Bekasi - Pusat Penjualan Besi Beton, Baja &amp; Baja Ringan Taso</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0812-9327-9807</t>
+          <t>0812-6226-6225</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1408,20 +1412,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jalan Jembatan Lima Raya No.127, RT.1/RW.4, Duri Utara, Kec. Tambora, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11270, Indonesia</t>
+          <t>Jl. Wibawa Mukti II No.69, RT.003/RW.005, Jatiasih, Kec. Jatiasih, Kota Bks, Jawa Barat 17423, Indonesia</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.histeel.co.id/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11908598550414660348&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=1945967216354572927&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1433,12 +1437,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PT. BAJA CITRA AGUNG</t>
+          <t>Toko Besi Top Baja</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(021) 22052909</t>
+          <t>0813-8561-3756</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1448,20 +1452,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jl. Gn. Merapi Jl. Taman Palem Mutiara No.D1/39 4, RT.4/RW.14, Cengkareng Tim., Kecamatan Cengkareng, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11730, Indonesia</t>
+          <t>Jl. Benda Raya No.94, Pd. Benda, Kec. Pamulang, Kota Tangerang Selatan, Banten 15416, Indonesia</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://www.topbaja.com/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2628839145996746920&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8495418184792653542&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1473,12 +1477,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pabrik Baja Girder Dan Erection</t>
+          <t>Hi Steel Tangerang</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0851-7504-5856</t>
+          <t>0813-9422-3333</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1488,20 +1492,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jl. Manunggal Jaya I No.69, RT.8/RW.4, Lb. Bulus, Kec. Cilandak, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12440, Indonesia</t>
+          <t>Jl. Siliwangi Depan PLN No.76, Benda Baru, Kec. Pamulang, Kota Tangerang Selatan, Banten 15416, Indonesia</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://histeel.co.id/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11116475033830380814&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12168439008341303587&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1513,12 +1517,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YJK Bengkel Las Kanopi Pagar Pintu Besi Konstruksi Baja Renovasi Rumah Kantor</t>
+          <t>PT Era Baja Mandiri</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0877-7516-0708</t>
+          <t>0831-2154-2562</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jl. Kamal Muara No.244, RT.7/RW.1, Kamal Muara, Kecamatan Penjaringan, Jkt Utara, Daerah Khusus Ibukota Jakarta 14470, Indonesia</t>
+          <t>Jl. Industri Raya I No.10 Blok H, RT.001/RW.004, Jatake, Kec. Jatiuwung, Kota Tangerang, Banten 15134, Indonesia</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1536,12 +1540,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://bit.ly/YakinJayaKonstruksi</t>
+          <t>https://erabajamandiri.com/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7504623769554357245&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=2001385226936890880&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1553,12 +1557,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PT. PARKASA WAJENDRA KARYA | Kontraktor Rumah, Hotel, Rumah Sakit, Baja, Gudang, Pabrik, Aspal, Design Interior, Furniture</t>
+          <t>PT. Baja Perkasa Multi Abadi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0818-808-683</t>
+          <t>(021) 55657669</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1568,20 +1572,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Equity Tower, Jl. Jend. Sudirman kav 52-53 Lt 49, RT.5/RW.3, Senayan, SCBD, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12190, Indonesia</t>
+          <t>Jl. Gatot Subroto Km 5 No.68 RT02, RT.003/RW.03, Keroncong, Kec. Jatiuwung, Kota Tangerang, Banten 15134, Indonesia</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>http://parkasa.co.id/</t>
+          <t>https://bajaperkasamultiabadi.com/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17843818259103282764&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=3310268429250034216&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1593,12 +1597,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tukang baja ringan murah</t>
+          <t>PT. Mitra Baja Persada - Roll Pipa &amp; Fabrikasi Tangki Tangerang</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0813-1524-4586</t>
+          <t>0888-0910-1112</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1608,20 +1612,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RT.4/RW.18, Sunter Agung, Sunter, North Jakarta City, Jakarta 14350, Indonesia</t>
+          <t>Jl. Gatot Subroto, RT.002/RW.001, Jatiuwung, Kec. Cibodas, Kota Tangerang, Banten 15138, Indonesia</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://go.mitrabaja.id/gmb-jati</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8197610627889072569&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=4092170547136632292&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1633,12 +1637,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jagat Konstruksi Abdipersada</t>
+          <t>PT Karya Baja Sukses</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(021) 56969178</t>
+          <t>0877-7436-9214</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1648,20 +1652,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jl. Tomang Raya No.28 5, RT.5/RW.1, Jatipulo, Kec. Palmerah, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11430, Indonesia</t>
+          <t>Jl. Industri Keroncong, RT.005/RW.023, Gebang Raya, Kec. Periuk, Kota Tangerang, Banten 15132, Indonesia</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>http://jagatkonstruksi.com/</t>
+          <t>http://www.karyabajasukses.com/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7907272005378775274&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=13042390816574278774&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1673,12 +1677,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PT Asia Baja Sentosa</t>
+          <t>PT. Baja Putih</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0818-1822-0808</t>
+          <t>(021) 5919027</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1688,7 +1692,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jl. H. Agus Salim No.57, RT.3/RW.1, Kb. Sirih, Kec. Menteng, Kota Jakarta Pusat, Daerah Khusus Ibukota Jakarta 10340, Indonesia</t>
+          <t>Jalan Baitu Sa'adah No.200, Kadu Wetan, Kec. Curug, Kabupaten Tangerang, Banten 15810, Indonesia</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1696,12 +1700,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://asiabajasentosa.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10628326238837017293&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8128591894994620099&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1713,12 +1717,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kontraktor Konstruksi - Baja Jakarta</t>
+          <t>PANCA BAJA TANGERANG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0889-8098-7201</t>
+          <t>0851-6358-8351</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jl. Pluit Mas Selatan IV, RT.3/RW.18, Pejagalan, Kecamatan Penjaringan, Jkt Utara, Daerah Khusus Ibukota Jakarta 14450, Indonesia</t>
+          <t>Jl. Moh. Toha No.9, RT.002/RW.007, Periuk, Kec. Periuk, Kota Tangerang, Banten 15131, Indonesia</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1736,12 +1740,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://www.tokopedia.com/pancabajatangerang?source=universe&amp;st=product</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13356128643645023867&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8271031561046759013&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1753,12 +1757,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PT INDO TRANS BAJAUTAMA</t>
+          <t>BAJA MAKMUR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0813-6176-0253</t>
+          <t>0812-8863-6369</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1768,20 +1772,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Summarecon Bekasi, Ruko Emerald, Jl. Bulevar Selatan, RT.004/RW.011, Marga Mulya, Kec. Bekasi Utara, Kota Bks, Jawa Barat 17142, Indonesia</t>
+          <t>Jl. Raya Merdeka No.336, RT.002/RW.002, Cimone Jaya, Kec. Karawaci, Kota Tangerang, Banten 15114, Indonesia</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.indotransbajautama.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=414084336352572376&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=16416621624840116379&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1793,12 +1797,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lab Uji Material Besi Baja &amp; Beton PT. Bintang Abestaton Mahesa</t>
+          <t>PT Saka Baja Metalindo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0812-6888-1882</t>
+          <t>(021) 59404849</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1808,20 +1812,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6, Jl. Laksamana Malahayati No.25, RT.6/RW.7, Cipinang Muara, Jatinegara, East Jakarta City, Jakarta 13420, Indonesia</t>
+          <t>Kawasan Industri, Jl. Raya Serang No.KM. 12, Sukadamai, Kec. Cikupa, Kabupaten Tangerang, Banten 15115, Indonesia</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.abestaton.com/</t>
+          <t>http://www.sakabajametalindo.co.id/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11750417879718849548&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5209493797940652664&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1833,12 +1837,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alfian Baja Summarecon Bogor</t>
+          <t>PT. Baja Karya Perkasa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0852-8390-3645</t>
+          <t>(021) 54345154</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1848,7 +1852,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jl. Perumahan Jl. Mutiara Bogor Raya No.Rt.07, RT.02/RW.16, Katulampa, Kec. Bogor Tim., Kota Bogor, Jawa Barat 16144, Indonesia</t>
+          <t>Rukan Great Wall, Jl. Green Lake City Boulevard No.96 Blk B, RT.002/RW.008, Gondrong, Kec. Cipondoh, Kota Tangerang, Banten 15146, Indonesia</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1856,12 +1860,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>http://alfianbaja.co.id/</t>
+          <t>http://www.bajakaryaperkasa.co.id/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5725059420882212361&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9775929105710661379&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PT Steel Natural Nusantara</t>
+          <t>PRIMA BAJAINDO SUKSES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>(021) 82488333</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1888,20 +1892,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Rt 01 Rw 01 Jalan Raya Setu km 0.7 Kp. Rawahinghkik, RT.001/RW.001, Limus Nunggal, Kec. Cileungsi, Kabupaten Bogor, Jawa Barat 16820, Indonesia</t>
+          <t>Jalan Raya Serang KM.10,5 NO.9, RT.001/RW.004, Kadu Jaya, Kec. Curug, Kabupaten Tangerang, Banten 15810, Indonesia</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>http://alambajanusantara.id/</t>
+          <t>https://www.primabajaindosukses.co.id/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10489725889753293396&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=4523476849062953830&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1913,12 +1917,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PT Kencana Maju Bersama Cabang Bogor</t>
+          <t>PT.Inter World Steel Mills Indonesia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0822-3428-0141</t>
+          <t>(021) 5918767</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1928,20 +1932,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jl. Raya Pemda Jl. Kedung Halang No.44, RT.05/RW.01, Kedunghalang, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16158, Indonesia</t>
+          <t>Jl. Palem Manis Raya, RT.005/RW.006, Gandasari, Kec. Jatiuwung, Kota Tangerang, Banten 15137, Indonesia</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>http://kencanaindonesia.co.id/</t>
+          <t>http://www.iwsteel.com/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16490482894153178600&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9930932615247620521&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1953,12 +1957,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PT.SARANA PUTRA BAJA</t>
+          <t>PT Baja Era Sukses</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>0821-6888-0199</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1968,7 +1972,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jl. Gn. Pancar No.54, Sumur Batu, Kec. Babakan Madang, Kabupaten Bogor, Jawa Barat 16810, Indonesia</t>
+          <t>Jl. Gatot Subroto Km 5 No.66B, RT.002/003, Keroncong, Kec. Jatiuwung, RT.003/RW.001, Keroncong, Kota, Kota Tangerang, Banten 15134, Indonesia</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1976,12 +1980,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://bajaerasukses.com/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=6750551841774131224&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11711025763651788033&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1993,12 +1997,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CAHAYA BAJA SHOLEH ISKANDAR</t>
+          <t>PT. SINAR BANGUN BAJA PRIMA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0812-1888-9996</t>
+          <t>0878-8878-8168</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2008,20 +2012,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jl. Sholeh Iskandar, RT.005/RW.004, Cibadak, Tanah Sareal, Kota Bogor, Jawa Barat 16166, Indonesia</t>
+          <t>Jl. Raya Merdeka No.285, RT.002/RW.3, Pabuaran, Kec. Karawaci, Kota Tangerang, Banten 15114, Indonesia</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://cahayabajaidn.com/</t>
+          <t>https://www.bajaprima.com/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7373076640490373154&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17323468611594183764&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2033,12 +2037,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mega Baja Bogor</t>
+          <t>PT.Baja Jaya Makmur Cemerlang</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0831-4624-7814</t>
+          <t>(021) 22306097</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2048,20 +2052,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jl. Raya Ks Tubun No.299, RT.01/RW.02, Ciluar, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16154, Indonesia</t>
+          <t>Jl. Yos Sudarso No.63, RT.003/RW.009, Jurumudi Baru, Kec. Benda, Kota Tangerang, Banten 15124, Indonesia</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.megabajabogor.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16342334384872982151&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5540436127358924643&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2073,12 +2077,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Langit indah baja Bogor</t>
+          <t>PT. BERLIAN BAJA NUSANTARA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0851-7681-6711</t>
+          <t>0813-8999-5199</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2088,11 +2092,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NO WA : O&amp;2I5OOO615, Ciderum, Kec. Caringin, Kabupaten Bogor, Jawa Barat 16730, Indonesia</t>
+          <t>Kws Industri Pergudangan Blessindo 2, Jl. H. Tabri No.228 Blok P11, Kp.Nagrek, Bojongkamal, Kec. Legok, Kabupaten Tangerang, Banten 15820, Indonesia</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17358695388640433673&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=3759710258748829361&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2113,12 +2117,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mega baja steel</t>
+          <t>PT Mitra Baja Sejahtera</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0896-7521-6740</t>
+          <t>(021) 59588289</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dekat Kaos &amp; Sablon (KMO, Jl. Raya Ciluar No.20A, RT.01/RW.09, Ciluar, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16157, Indonesia</t>
+          <t>Ruko, Edison Raya Jl. Raya Boulevard Permata Medang No.3 Blk C, Medang, Kec. Pagedangan, Kabupaten Tangerang, Banten 15334, Indonesia</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2136,12 +2140,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://wa.me/6289675216740</t>
+          <t>http://mitrabajasejahtera.co.id/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7492073232011456331&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9699904704482436877&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2153,12 +2157,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PT BESI BAJA SEJAHTERA</t>
+          <t>PT. Kurnia Besi Baja</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>0812-1345-8651</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2168,20 +2172,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FRPQ+98X, Nanggewer, Cibinong, Bogor Regency, West Java 16912, Indonesia</t>
+          <t>Ruko Alicante Blok A no 38, Ruko Alicante, Jl. Jenderal Gatot Subroto, Medang, Kec. Pagedangan, Kabupaten Tangerang, Banten 15334, Indonesia</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://kurniabesibaja.com/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=9496370012114753735&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=831139340218393165&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2193,12 +2197,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Toko Besi Baja Mulia Bersinar</t>
+          <t>PT.POWER STEEL MANDIRI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0877-8687-0098</t>
+          <t>5916 5225</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2208,11 +2212,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Jl. KH. R. Abdullah Bin Nuh, RT.05/RW.04, Cibadak, Kec. Bogor Bar., Kota Bogor, Jawa Barat 16114, Indonesia</t>
+          <t>QF3W+F5J, Millennium industrial Estate, Peusar, Kec. Panongan, Kabupaten Tangerang, Banten 15710, Indonesia</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2221,7 +2225,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=14732762128103270614&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=142490398461806141&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2233,12 +2237,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mega Baja Ciawi</t>
+          <t>PT Kencana Maju Bersama Cabang Tangerang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0851-1747-8474</t>
+          <t>0822-3428-0150</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2248,20 +2252,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jl. Raya Sukabumi No.05, RT.01/RW.08, Harjasari, Kec. Bogor Sel., Kota Bogor, Jawa Barat 16138, Indonesia</t>
+          <t>Jl. Raya Serang No.110, Bunder, Kec. Cikupa, Kabupaten Tangerang, Banten 15710, Indonesia</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.megabajaciawi.com/</t>
+          <t>http://kencanaindonesia.co.id/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11001998880215481285&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9945364615319512951&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2273,12 +2277,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PT. Binangkit Baja Mulya</t>
+          <t>PT Bangun Era Sejahtera Mandiri</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>(021) 29412100</t>
+          <t>(021) 55656779</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2288,20 +2292,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Blok E4 No.4, Jl. Raya Bilabong Permai, Cimanggis, Kecamatan Bojonggede, Kabupaten Bogor, Jawa Barat 16920, Indonesia</t>
+          <t>Jl. Palem Manis 2 No.88, RT.003/RW.006, Gandasari, Kec. Jatiuwung, Kota Tangerang, Banten 15137, Indonesia</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>http://binangkitbaja.com/</t>
+          <t>https://besm.co.id/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17313983107518947200&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=297882213209687655&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2313,12 +2317,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Juan1908 team</t>
+          <t>PT Mitra Logam Pratama Steel Factory</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0857-1785-6702</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2328,11 +2332,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jl. Cimanggu Barata, RT.07/RW.09, Kedungbadak, Kec. Bogor Sel., Kota Bogor, Jawa Barat 16164, Indonesia</t>
+          <t>Mitra Logam Pratama Steel Factory Pt., Jl. Raya Ps. Kemis No.8, Gelam Jaya, Kec. Ps. Kemis, Kabupaten Tangerang, Banten 15560, Indonesia</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2341,7 +2345,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16032111590442329458&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=13844028932532235743&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2353,12 +2357,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mega Baja Steel</t>
+          <t>PT. Xin Yuan Steel</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0878-8902-8965</t>
+          <t>(021) 5952555</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2368,20 +2372,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Dekat, RT.03/RW.01, Cibuluh, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16151, Indonesia</t>
+          <t>Jl. Raya Serang No.25.5 No.KM, Sentul Jaya, Kec. Balaraja, Kabupaten Tangerang, Banten 15610, Indonesia</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://wa.me/qr/Z6P6UILO5FTEA1</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13003830352023890885&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=15815024118175853288&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2393,12 +2397,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PT Berdikari Tunggal Perkasa</t>
+          <t>PT. Togo Steel Industries</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0811-1000-379</t>
+          <t>(021) 59317060</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2408,20 +2412,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FVW5+2QG, Jl. Lanbau, Sentul, Kec. Citeureup, Kabupaten Bogor, Jawa Barat 16810, Indonesia</t>
+          <t>Kawasan Industri GKBI Jalan Raya Kutabumi No.01 Karet Sepatan, Karet, Kec. Periuk, Kabupaten Tangerang, Banten 15131, Indonesia</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>http://www.supplieratap.com/</t>
+          <t>http://www.togosteel.co.id/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11455244718021616585&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7794378720772928228&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2433,12 +2437,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bengkel Las RCS Baja</t>
+          <t>Shan Fu Metal Industry. PT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0857-1751-9764</t>
+          <t>(021) 5988358</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2448,11 +2452,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jalan Gapura Cijujung No.RT 02/02, Jembatan Dua Raja, Kec. Sukaraja, Kabupaten Bogor, Jawa Barat 16710, Indonesia</t>
+          <t>km 03, Jl. Raya PLP Curug Jl. Kp. Onyam, Kadu, Kec. Curug, Kabupaten Tangerang, Banten 15318, Indonesia</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2461,7 +2465,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17832548862254584325&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5193726783569023810&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2473,12 +2477,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bamboo Zet</t>
+          <t>CV. Sethindo Baja Makmur</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>(021) 55654456</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2488,7 +2492,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Gg. Mesjid Gg. Al-Falah No.16, RT.02/RW.18, Cilendek Bar., Kec. Bogor Bar., Kota Bogor, Jawa Barat 16112, Indonesia</t>
+          <t>Jl. Telesonik, Kadu Jaya, Kec. Curug, Kabupaten Tangerang, Banten 15810, Indonesia</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2496,12 +2500,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.sethindobajamakmur.com/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13422844963527678052&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11452830401172778425&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2513,12 +2517,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mega Baja Sentul</t>
+          <t>PT Prima Baja Indonesia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0851-1752-8474</t>
+          <t>(021) 21789599</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2528,20 +2532,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Jl. Sentul Raya, RT.01/RW.02, Cipambuan, Kec. Babakan Madang, Kabupaten Bogor, Jawa Barat 16810, Indonesia</t>
+          <t>Blok A Kawasan Industri Jl. Industri Raya No.8, RT.2/RW.2, Jatake, Kec. Jatiuwung, Kota Tangerang, Banten 15136, Indonesia</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://megabajasentul.com/</t>
+          <t>http://www.primabajaindonesia.com/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=679024979800483734&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5788720221194172128&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2553,12 +2557,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BAJA RINGAN TASO - TK. CAKRAWALA</t>
+          <t>PT. Cahaya Bekasi Bajatama</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0816-225-999</t>
+          <t>(021) 88960880</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2568,20 +2572,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>bekas kantor BPJS lama, Jl. Sholeh Iskandar No.10, RT.01/RW.06, Kedungbadak, Tanah Sareal, Kota Bogor, Jawa Barat 16710, Indonesia</t>
+          <t>Jl. Sultan Agung No.KM 27 No.5, RT.004/RW.007, Medan Satria, Kecamatan Medan Satria, Kota Bks, Jawa Barat 17133, Indonesia</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://tokopedia.link/tokocakrawalabogor</t>
+          <t>http://www.cbbsteel.id/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=3924858844072917140&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=10098007250745485504&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2593,12 +2597,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAHAYA BAJA CIOMAS</t>
+          <t>PT. Cilegon Steel Indonesia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0823-3535-0099</t>
+          <t>0812-9179-5555</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2608,20 +2612,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jl Raya Ciomas, Cikoneng Kecamatan No.001, RT.001/RW.006, Padasuka, Kec. Ciomas, Kabupaten Bogor, Jawa Barat 16610, Indonesia</t>
+          <t>Jalan Raya Narogong No.9 Rawa Lumbu, RT.001/RW.001, Sepanjang Jaya, Kec. Rawalumbu, Kota Bks, Jawa Barat 17116, Indonesia</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://cahayabajaidn.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=3587183907406660159&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=14079978697609995393&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2633,12 +2637,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kontraktor Jasa Renovasi Rumah Bogor | Arsitek &amp; Tukang Pemborong Bangunan di Bogor</t>
+          <t>Wira Karya Adiperkasa PT, Distributor Besi, Baja, Sekrup dsb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0813-9945-2700</t>
+          <t>0821-2479-2422</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2648,11 +2652,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jl. Arzimar Gang Kepunduhan 1 No.2, RT.001/RW.018, Tegal Gundul, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16152, Indonesia</t>
+          <t>Jl. H. Djole, RT.001/RW.009, Padurenan, Kec. Bantar Gebang, Kota Bks, Jawa Barat 17151, Indonesia</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2661,7 +2665,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13919113364655468879&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17988515282081902773&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2673,12 +2677,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PT. Pancar Teknik</t>
+          <t>PT. Bintang Mutiara Tangguh</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0898-9452-367</t>
+          <t>(021) 84970905</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2688,11 +2692,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Jl. Menteng No.74, RT.01/RW.04, Menteng, Kec. Bogor Bar., Kota Bogor, Jawa Barat 16111, Indonesia</t>
+          <t>Jl. Raya Kodau No.16, RT.002/RW.013, Jatimakmur, Kec. Pd. Gede, Kota Bks, Jawa Barat 17413, Indonesia</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2701,7 +2705,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5894223640554859432&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8023147115360497881&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2713,12 +2717,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kontraktor Bogor (TKP &amp; DESRUM)</t>
+          <t>PT. Bajamas Perkasa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0857-8240-5387</t>
+          <t>(021) 8204009</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2728,11 +2732,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Jl. Taman Sari Persada No.6 Blok E3, RT.04/RW.15, Cibadak, Tanah Sareal, Kota Bogor, Jawa Barat 16168, Indonesia</t>
+          <t>Jl. Raya Siliwangi No.15, RT.002/RW.003, Sepanjang Jaya, Kec. Rawalumbu, Kota Bks, Jawa Barat 17114, Indonesia</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2741,7 +2745,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=1208947952188378272&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12575945396528140886&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2753,12 +2757,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jasa Tukang Rumah</t>
+          <t>MITRA BAJA BEKASI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0819-1117-8398</t>
+          <t>0812-1979-1389</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2768,7 +2772,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Nirwana Golden Park Blok C2 No.12, Pakansari, Kec. Cibinong, Kabupaten Bogor, Jawa Barat 16915, Indonesia</t>
+          <t>Jl. Karang Satria, RT.001/RW.008, Duren Jaya, Kec. Bekasi Tim., Kota Bks, Jawa Barat 17111, Indonesia</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2776,12 +2780,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>http://www.jasatukangrumah.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8472665152153306598&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=6195888378457242061&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2793,12 +2797,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RHI Build jasa kontraktor profesional</t>
+          <t>Dunia Baja Komsen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>0813-8484-8351</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2808,20 +2812,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Jl. Sempur Kaler No.25, RT.03/RW.02, Sempur, Kecamatan Bogor Tengah, Kota Bogor, Jawa Barat 16129, Indonesia</t>
+          <t>Komsen, Jl. Wibawa Mukti No.45A, RT.003/RW.005, Jatiasih, Kec. Jatiasih, Kota Bks, Jawa Barat 17423, Indonesia</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://rhi-build.id/</t>
+          <t>https://duniabajakomsen.com/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17694682007872886554&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=13534124020675486590&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2833,12 +2837,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tukang bangunan, renovasi rumah, dan kontraktor bangunan bogor</t>
+          <t>PT. Toyogiri Iron Steel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0812-1926-7915</t>
+          <t>(021) 8804613</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2848,20 +2852,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kp Gg. Jampang Pulo No.03, RT.03, Jampang, Kec. Kemang, Kabupaten Bogor, Jawa Barat 16310, Indonesia</t>
+          <t>Jl. Toyogiri Sel. No.38, Jatimulya, Kec. Tambun Sel., Kabupaten Bekasi, Jawa Barat 17510, Indonesia</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.toyogiristeel.com/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7293912325265031722&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=6193344572536278142&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2873,12 +2877,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jasa Tukang Bangunan dan Renovasi CV Abdi Home</t>
+          <t>Pabrik Besi dan Baja</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0878-7472-2911</t>
+          <t>0838-4170-2248</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2888,20 +2892,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Jl. Muara Peundeuy, RT.01/RW.11, Sindangrasa, Kec. Bogor Tim., Kota Bogor, Jawa Barat 16145, Indonesia</t>
+          <t>Ispat Bukit Baja Pt., Jl. Raya Perjuangan No.24, RT.002/RW.009, Marga Mulya, Kec. Bekasi Utara, Kota Bks, Jawa Barat 17142, Indonesia</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>http://www.sugandihome.com/</t>
+          <t>http://www.ispatindo.com/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8114688755826072267&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8983619499585962914&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2913,12 +2917,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PT. Krima Karya Solusi</t>
+          <t>PT. Honglu Konstruksi Baja / PT. Honglu Baja Indonesia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>(0251) 2020181</t>
+          <t>0823-5296-6666</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2928,20 +2932,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ruko Bogor Indah Raya, Jl. Sholeh Iskandar No.7 Blok A, RT.05/RW.08, Kedungbadak, Tanah Sareal, Kota Bogor, Jawa Barat 16164, Indonesia</t>
+          <t>Jl. Jarakosta No.256, RT.05/RW.02, Sukadanau, Kec. Cikarang Bar., Kabupaten Bekasi, Jawa Barat 17520, Indonesia</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://krimakaryasolusi.co.id/</t>
+          <t>http://honglu.id/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=14519198199868069147&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12555389732087349960&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2953,12 +2957,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jasa Kontraktor di Bogor ( CV.Bersama Bangun Sejahtera)</t>
+          <t>PT. Bintang Baja Sejahtera</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0812-2648-0550</t>
+          <t>(021) 8853671</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2968,20 +2972,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pondok Udik, Kemang, Bogor Regency, West Java 16310, Indonesia</t>
+          <t>Jl. Sultan Agung, RT.001/RW.001, Kali Baru, Kecamatan Medan Satria, Kota Bks, Jawa Barat 17132, Indonesia</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>http://renovrumahbogor.id/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17125516174664148427&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9483770534118319869&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2993,12 +2997,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mulia Arsitek Kontraktor Bogor</t>
+          <t>Tria Baja Utama</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0811-2648-986</t>
+          <t>0813-1312-966</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3008,20 +3012,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Jl. Pasir Mulya 3 No.L.12, RT.02/RW.07, Pasirmulya, Kec. Bogor Bar., Kota Bogor, Jawa Barat 16118, Indonesia</t>
+          <t>Jl. Teuku Umar No.106, RT.004/RW.001, Sepanjang Jaya, Kec. Rawalumbu, Kota Bks, Jawa Barat 17114, Indonesia</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://muliaarsitek.com/</t>
+          <t>https://msha.ke/triabajautama</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5594205340501110188&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=15589036578721739652&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3033,12 +3037,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>The Mutiara Bogor</t>
+          <t>PT.Karyabenteng Barusemesta Bekasi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(0251) 2020283</t>
+          <t>(021) 8894747</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3048,20 +3052,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Jl. Bogor Raya City, RT.03/RW.02, Katulampa, Kec. Bogor Tim., Kota Bogor, Jawa Barat 10160, Indonesia</t>
+          <t>Jl. Sultan Agung No.7, RT.006/RW.022, Kota Baru, Kec. Bekasi Bar., Kota Bks, Jawa Barat 17132, Indonesia</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://themutiarabogor.com/</t>
+          <t>http://www.karyabenteng.com/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5429026322465119974&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=2511652275532497206&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3073,12 +3077,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PT BERLIAN KONTRAKTOR</t>
+          <t>Sampoerna Jaya Baja PT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0857-1591-0161</t>
+          <t>(021) 82604609</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3088,7 +3092,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Jl. Palayu Raya No.2, RT.5/RW.10, Tegal Gundil, Kec. Bogor Utara, RT.02/RW.10, Tegal Gundil, Kota, Kota Bogor, Jawa Barat 16152, Indonesia</t>
+          <t>RT.001/RW.003, Cikiwul, Kec. Bantar Gebang, Kota Bks, Jawa Barat 17152, Indonesia</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3096,12 +3100,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://berliankontraktor.com/</t>
+          <t>https://www.sampoernajayabaja.com/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=478812090704526381&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=3673538932376508994&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3113,12 +3117,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SIPINTAR GENERAL CONTRACTOR</t>
+          <t>PT. CIPTA BAJA REKAYASA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0822-3100-0142</t>
+          <t>(021) 28519001</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3128,20 +3132,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Jl. Ceger permai, Jl. Pamikul Bawah Jl. Villa Citra No.perum, RT.04/RW.17, Tegal Gundil, Kec. Bogor Utara, Kota Bogor, Jawa Barat 16152, Indonesia</t>
+          <t>Grand Permata Bussiness Park, Jl. Ahmad Yani Jl. Raya Pekayon No.1 Blk A-11, RT.005/RW.002, Pekayon Jaya, Kec. Bekasi Sel., Bekasi Selatan, Jawa Barat 17148, Indonesia</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://www.sipintar-contractor.com/</t>
+          <t>http://ciptabaja.com/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2574432723270861238&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11810787231210370337&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3153,12 +3157,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SADAR BANGUN ( KONTRAKTOR BOGOR )</t>
+          <t>Pt. Baja Marga Prima Persada</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0813-1960-2108</t>
+          <t>(021) 88851133</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3168,20 +3172,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Jl. Muara Tegal, RT.02/RW.01, Sindangrasa, Kec. Bogor Tim., Kota Bogor, Jawa Barat 16145, Indonesia</t>
+          <t>Jl. Sultan Agung No.KM.28 No.150, RT.002/RW.001, Medan Satria, Kecamatan Medan Satria, Kota Bks, Jawa Barat 17132, Indonesia</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.sadarbangun.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11341257527210260366&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7686295674657650907&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3193,12 +3197,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BIG KONTRAKTOR</t>
+          <t>PT Ispat Bukit Baja</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0811-1900-056</t>
+          <t>(021) 8840519</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3208,11 +3212,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Jl. Cilendek Indah IV No.51, RT.02/RW.16, Cilendek Bar., Kec. Bogor Bar., Kota Bogor, Jawa Barat 16112, Indonesia</t>
+          <t>Jl. Perjuangan Raya No.26, RT.003/RW.009, Marga Mulya, Kec. Bekasi Utara, Kota Bks, Jawa Barat 17142, Indonesia</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13640222940047739297&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=15969680269870653712&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3233,12 +3237,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>design and build, bangun baru, renovasi, interior, arsitekur, punakawan urban development</t>
+          <t>PT Kencana Maju Bersama Cabang Bekasi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0822-9929-8673</t>
+          <t>0822-3428-4160</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3248,7 +3252,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Jl. Ring Road Jl. Raya Bubulak No.A-4, RT.01/RW.11, Bubulak, Kec. Bogor Bar., Kota Bogor, Jawa Barat 16115, Indonesia</t>
+          <t>Jalan Raya Narogong No.km. 6 No. 74, RT.003/RW.002, Bojong Rawalumbu, Kec. Rawalumbu, Kota Bks, Jawa Barat 17116, Indonesia</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3256,12 +3260,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://punakawanbuild.com/</t>
+          <t>http://kencanaindonesia.co.id/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=1398449662082853689&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=16576003739216555870&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3273,12 +3277,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PT. Asiakons Engineering Indonesia</t>
+          <t>Mega Baja Bantar Gebang</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0852-1881-0540</t>
+          <t>0812-2224-8474</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3288,20 +3292,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Blok i Jl. Baranangsiang III No.7, RT.05/RW.08, Tegallega, Kecamatan Bogor Tengah, Kota Bogor, Jawa Barat 16129, Indonesia</t>
+          <t>Jl. Raya Narogong Jl. Raya Bekasi, RT.004/RW.004, Bojong Menteng, Kec. Rawalumbu, Kota Bks, Jawa Barat 17310, Indonesia</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>http://www.asiakons.id/</t>
+          <t>http://www.megabajabantargebang.com/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2855641901931347004&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9968413159517693449&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3313,12 +3317,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CV.EMASNA PROPERTINDO SENTOSA (CV.EMPROS) contractor-Architech-General Trade</t>
+          <t>Jasa Pasang Baja (Ringan/Full) Konstruksi "Baja'na Bekasi"</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0813-8911-3085</t>
+          <t>0857-7189-3310</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3328,7 +3332,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jl. Mekar Jaya No.14,15, Mekarjaya, Kec. Ciomas, Kabupaten Bogor, Jawa Barat 16610, Indonesia</t>
+          <t>Komplek Masnaga Jl. Dempo No.183 Blok.A, RT.009/RW.009, Jakasampurna, Kec. Bekasi Bar., Kota Bks, Jawa Barat 17145, Indonesia</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3336,12 +3340,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.empros.co.id/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=13779199134978926136&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=3429099101764847676&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3353,12 +3357,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TOKO PVC Sungkay jaya cibinong Bogor</t>
+          <t>PT. KONSTRUKSI BAJA UTAMA (KBU)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0882-9098-2010</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3368,7 +3372,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jl. Raya Pajajaran, RT.01/RW.05, Bantarjati, Kecamatan branang siang, Kota Bogor, Jawa Barat 16936, Indonesia</t>
+          <t>Jl. Raya Ps. Muara No.23, Muarabakti, Kec. Babelan, Kabupaten Bekasi, Jawa Barat 17610, Indonesia</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=15268829228601422982&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11198674441792812219&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3393,12 +3397,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jasa Renovasi dan Bangun Rumah Profesional, Amanah, Harga Terjangkau JABODETABEK</t>
+          <t>JASA PASANG BAJA RINGAN (KINGS BAJARINGAN KONSTRUKSI RANGKA ATAP BAJA RINGAN dan PLAVON)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0813-2973-0293</t>
+          <t>0853-8383-2013</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3408,11 +3412,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Jl. Komp. Mina Bhakti No.126b, RT.06/RW.03, Kp. Parung Jambu, Cikaret, Kec. Bogor Sel., Kota Bogor, Jawa Barat 16132, Indonesia</t>
+          <t>Jl. Raya Hankam No.8, RT.004/RW.002, Jatirahayu, Kec. Pd. Melati, Kota Bks, Jawa Barat 17414, Indonesia</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3421,7 +3425,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=15173597773207908249&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12231142037929684139&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3433,12 +3437,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mega Baja Depok</t>
+          <t>tukang bale</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0813-1947-2550</t>
+          <t>0895-1547-0045</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3448,20 +3452,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Jl. Raya Sawangan Depok No.57, Rangkapan Jaya Baru, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16434, Indonesia</t>
+          <t>62, Jl. Mustika Jaya No.62, RT.003/RW.007, Mustikajaya, Kec. Mustika Jaya, Kota Bks, Jawa Barat 17158, Indonesia</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>http://www.megabajadepok.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=4276577797895359852&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=15415312261763760888&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3473,12 +3477,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mega Baja</t>
+          <t>PT. GUNUNG BAJA KONSTRUKSI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(021) 77833353</t>
+          <t>(021) 8901580</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3488,11 +3492,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jl. Raya Parung Serab (KSU) No.30, Tirtajaya, Kec. Sukmajaya, Kota Depok, Jawa Barat 16412, Indonesia</t>
+          <t>Jl. Jarakosta No.RT. 05/02, Sukadanau, Kec. Cikarang Bar., Kabupaten Bekasi, Jawa Barat 17520, Indonesia</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=632713848942757523&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=4559666052137138685&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3513,12 +3517,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Distributor Besi &amp; Baja Ringan CV Karya Indo</t>
+          <t>Dyan Baja Construction</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0812-1373-1600</t>
+          <t>0852-2775-5277</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3528,20 +3532,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Jl. Radar Auri No.115, Mekarsari, Kec. Cimanggis, Kota Depok, Jawa Barat 16452, Indonesia</t>
+          <t>Jl. Bonang III No.100, RT.005/RW.007, Jatirasa, Kec. Jatiasih, Kota Bks, Jawa Barat 17424, Indonesia</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>http://karyaindobaja.com/</t>
+          <t>https://dyanbajaconstruction.com/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8562611429512287752&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=13068134296458346027&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3553,12 +3557,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PABRIK PAGAR BRC - WIREMESH - KAWAT HARMONIKA</t>
+          <t>Konstruksi baja</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0811-9920-523</t>
+          <t>0812-8378-0100</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3568,11 +3572,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jl. Gg. Bacang No.43, Sukatani, Kec. Tapos, Kota Depok, Jawa Barat 16454, Indonesia</t>
+          <t>Plaza thb lt 2 no 17, RT.007/RW.025, Pejuang, Kecamatan Medan Satria, Kota Bks, Jawa Barat 17131, Indonesia</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3581,7 +3585,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=11743275078908187876&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=9977115767974991414&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3593,12 +3597,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mega Baja Cimanggis</t>
+          <t>RKPM (Rancang Konstruksi Perkasa Mandiri) KONTRAKTOR BAJA Spesialis Struktur Baja dan Mezzanine Kalsi, GRC, RB Shera</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0812-2880-8351</t>
+          <t>0812-4760-1080</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3608,20 +3612,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Jl. Raya Bogor Rt.Rw 002/001 Kelurahan Tugu Kecamatan Cimanggis Kota Depok, Tugu, Kec. Cimanggis, Kabupaten Bogor, Jawa Barat 16451, Indonesia</t>
+          <t>Jl. Parpostel No.km 15, RT.003/RW.001, Jatiluhur, Kec. Jatiasih, Kota Bks, Jawa Barat 17425, Indonesia</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>http://www.megabajacimanggis.com/</t>
+          <t>http://www.rkpm-indo.id/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5867590318059582687&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11643386025617588713&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3633,12 +3637,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TB. Depo Baja</t>
+          <t>PT. UTAMA CONSTRUCTION STEEL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0821-1389-8982</t>
+          <t>Tidak ada telepon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3648,11 +3652,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Jl. Raya Kp. Sawah, Jatimulya, Kec. Cilodong, Kota Depok, Jawa Barat 16413, Indonesia</t>
+          <t>QX54+WCC, Jl. Raya Kp. Setu, RT.001/RW.002, Bintara Jaya, Kec. Bekasi Bar., Kota Bks, Jawa Barat 17136, Indonesia</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3661,7 +3665,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17558133374891463304&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7988485088527463842&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3673,12 +3677,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fitrah Baja 165 depok</t>
+          <t>Galaxy Persada</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0822-9938-9999</t>
+          <t>(021) 8203156</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3688,20 +3692,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jl. Raya Parung No.37, Curug, Kec. Bojongsari, Kota Depok, Jawa Barat 16516, Indonesia</t>
+          <t>Jl. Cikunir Raya No.20, RT.003/RW.003, Jakamulya, Kec. Jatiasih, Kota Bks, Jawa Barat 17422, Indonesia</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.galaxypersada.com/</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2004940062256991980&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=10185113687001073459&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3713,12 +3717,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mega Baja Steel</t>
+          <t>PT .Eza Karya Berjaya. Mengerjakan Kontruksi Baja Dan Pembangunan Rumah</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0889-7135-3530</t>
+          <t>0813-1509-5031</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3728,7 +3732,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Dekat, Jl. Kartini No.60d, Depok, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16431, Indonesia</t>
+          <t>Jl. Lapangan Jl. Nayar 2, RT.004/RW.012, Kranji, Kec. Bekasi Bar., Kota Bks, Jawa Barat 17135, Indonesia</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -3741,7 +3745,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=8935728315488440422&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5494435361626486183&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3753,12 +3757,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GASmart Project - Pusat Baja &amp; Besi</t>
+          <t>PT Artama Anugrah Konstruksi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0811-8862-588</t>
+          <t>0812-8629-1034</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3768,7 +3772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jl. Bahagia Raya No.12, Abadijaya, Kec. Sukmajaya, Kota Depok, Jawa Barat 16417, Indonesia</t>
+          <t>Gg. Bambu Hideung No.35, RT.005/RW.001, Cikiwul, Kec. Bantar Gebang, Kota Bks, Jawa Barat 17152, Indonesia</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3776,12 +3780,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://artamaanugrahkontruksi.com/</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=15976773937275081128&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=10692657574328761970&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3793,12 +3797,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mega Baja Sawangan</t>
+          <t>Bengkel Las Berkah Jaya Sampurna 2 - Pagar, Tralis, Kanopi, Balkon, Railing Tangga | Bekasi &amp; Jakarta</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0813-9902-0744</t>
+          <t>0858-1126-6055</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3808,20 +3812,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jl. Raya Parung - Ciputat No.88, RT.01/RW.09, Kedaung, Kec. Sawangan, Kota Depok, Jawa Barat 16516, Indonesia</t>
+          <t>Jl. H. Ledang No.27, RT.003/RW.003, Sepanjang Jaya, Kec. Rawalumbu, Kota Bks, Jawa Barat 17174, Indonesia</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>http://www.megabajasawangan.com/</t>
+          <t>https://berkahjayasampurna.github.io/</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=7190949042913509212&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=6587696909017017717&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3833,12 +3837,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pabrikasi Pagar BRC, Wiremesh, Chainlink, Pallet Mesh Depok</t>
+          <t>Euphron Steel Construction / Jasa Konstruksi Baja</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0877-8699-8626</t>
+          <t>0822-4170-4534</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3848,20 +3852,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jl. Markisa III No.8 Blok E3, Sukatani, Kec. Tapos, Kota Depok, Jawa Barat 16454, Indonesia</t>
+          <t>Per.mayang Pratama blok G6 no3 RT015/RW08 kel, RT.013/RW.008, Mustikasari, Kec. Mustika Jaya, Kota Bks, Jawa Barat 17157, Indonesia</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>http://trimitrabaru.co.id/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=5285614144616382005&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=2911826845494784582&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3873,12 +3877,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CV Mustika Jaya Baja</t>
+          <t>PT Prima Sari Baja (Toko Besi Prima)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0815-1424-3682</t>
+          <t>0819-3281-6060</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jl. Raya Parung Bingung No.33, RT.003/RW.04, Rangkapan Jaya Baru, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16434, Indonesia</t>
+          <t>Jl. H. Bokir Bin Dji'un No.11, RT.4/RW.1, Dukuh, Kec. Kramat jati, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13550, Indonesia</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3896,12 +3900,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://cvmustikajayabaja.com/</t>
+          <t>Tidak ada website</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=1687091561010091508&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17124167604939022868&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3913,12 +3917,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CMS BAJA SUKSES</t>
+          <t>Hi Steel</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0821-1374-2803</t>
+          <t>0812-8440-2000</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jl. Tanah Baru No.5, RT.02/RW.06, Tanah Baru, Kecamatan Beji, Kota Depok, Jawa Barat 16426, Indonesia</t>
+          <t>Jl. Raya Jatiwaringin No.58, RT.007/RW.009, Jaticempaka, Kec. Pd. Gede, Kota Bks, Jawa Barat 17411, Indonesia</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3936,12 +3940,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://ciptamitraselaras.co.id/</t>
+          <t>https://histeel.co.id/</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10393793606531608596&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=8255418499727257393&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3953,12 +3957,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Inti Baja Pratama Kukusan</t>
+          <t>DISTRIBUTOR, Krakatau Steel, KS,</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>0812-8871-1562</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3968,20 +3972,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Jl. Kukusan Raya No.42, Kukusan, Kecamatan Beji, Kota Depok, Jawa Barat 16425, Indonesia</t>
+          <t>Jl. Ciledug Raya No.53f, RT.6/RW.4, Petukangan Sel., Kec. Pesanggrahan, Kota Jakarta Selatan, Daerah Khusus Ibukota Jakarta 12260, Indonesia</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://www.aneka-besi-baja.com/</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=6731352423547432061&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=14195126958735237006&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3993,12 +3997,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cmj Steel</t>
+          <t>Sumber Baja Indonesia - Distributor Besi | Baja Ringan I Plafon Pvc</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0877-8323-2388</t>
+          <t>0851-7324-7734</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4008,11 +4012,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jl. Raya Pahlawan No.92 A, RT.001/RW.002, Cinangka, Kec. Sawangan, Kota Depok, Jawa Barat 16516, Indonesia</t>
+          <t>Jl. Cikunir Raya No.8A, RT.008/RW.011, Jatimekar, Kec. Jatiasih, Kota Bks, Jawa Barat 17423, Indonesia</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4021,7 +4025,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16785774116183944660&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=1593856628790814908&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4033,12 +4037,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PT. SURA BAJA JAYA ABADI</t>
+          <t>TOKO BESI BAJA NUSANTARA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0857-1065-2297</t>
+          <t>0821-3333-8474</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4048,11 +4052,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Jl. Kampung Bedahan No.1, Kalibaru, Kec. Cilodong, Kota Depok, Jawa Barat 16414, Indonesia</t>
+          <t>Jl. Raya Jatikramat No.20, RT.007/RW.009 Kel, Jatikramat, Kec. Jatiasih, Kota Bks, Jawa Barat 17421, Indonesia</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4061,7 +4065,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=6645147499450084460&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=11000461332974188748&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4073,12 +4077,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Toko Besi Bintang Baja</t>
+          <t>PT DEPO BAJA STEELINDO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0878-8106-7766</t>
+          <t>0878-9402-4997</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4088,20 +4092,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Jl. Tanah Baru No.101, Beji, Kecamatan Beji, Kota Depok, Jawa Barat 16426, Indonesia</t>
+          <t>Jl. Semanan Raya No.88B, RT.10/RW.8, Semanan, Kec. Kalideres, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11850, Indonesia</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://indobesibaja.com/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=12227635789088671790&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=13297862288796621170&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4113,12 +4117,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLAFON PVC GUNUNG BAJA CABANG DEPOK</t>
+          <t>Raja Besi (Sultan Agung, Km 28,5) _ Distributor Besi, Baja Ringan, Spandek, dan Aksesoris</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0823-1885-6184</t>
+          <t>0851-7311-4543</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4128,11 +4132,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Jl. Kartini No.38A, Depok, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16431, Indonesia</t>
+          <t>Jl. Sultan Agung No.Km. 28, 5, RT.007/RW.003, Medan Satria, Kecamatan Medan Satria, Kota Bks, Jawa Barat 17132, Indonesia</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4141,7 +4145,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2345127233458565573&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17073780984616535570&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4153,12 +4157,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Satria Baja</t>
+          <t>Toko Besi Sinar Baja Mandiri</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>(021) 87757474</t>
+          <t>0812-9680-0438</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4168,11 +4172,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>JVHC+2C9, Jl. Radar Auri, Mekarsari, Kec. Cimanggis, Kota Depok, Jawa Barat 16454, Indonesia</t>
+          <t>Jalan Raya Benteng Betawi, Jl. Taman Royal 3 Jl. Pinus III No.5, RT.002/RW.010, Poris Plawad, Kec. Cipondoh, Kota Tangerang, Banten 15141, Indonesia</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4181,7 +4185,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=16323549261603073828&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5345385913783462416&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4193,12 +4197,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PT. JAYA BHAKTI UTOMO</t>
+          <t>Mega Baja Ciledug</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0878-4448-5244</t>
+          <t>0811-1968-474</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4208,20 +4212,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Jl. Mawar 3 No.109, Depok Jaya, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16432, Indonesia</t>
+          <t>Jl. Ciledug Raya No.11, RT.1/RW.3, Petukangan Sel., Kec. Pesanggrahan, Kota Jakarta Selatan, Banten 12270, Indonesia</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://jayabhaktiutomo.com/</t>
+          <t>http://www.megabajaciledug.com/</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=10808686204585128575&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=7645100584370411393&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4233,12 +4237,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>baja ringan depok</t>
+          <t>Toko Besi Citra Baja</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tidak ada telepon</t>
+          <t>0812-9057-0222</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4248,11 +4252,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Gg. H. Sain No.73, Kalibaru, Kec. Cilodong, Kota Depok, Jawa Barat 16473, Indonesia</t>
+          <t>Jl. Raya Jatimulya, RT.004/RW.003, Pengasinan, Kec. Bekasi Tim., Kota Bks, Jawa Barat 17115, Indonesia</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4261,7 +4265,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=2565816833926485187&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17715784297957237131&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4273,12 +4277,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Distributor + toko baja ringan oerlikon truss</t>
+          <t>Mega Baja Duren Sawit</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0812-9600-880</t>
+          <t>0813-4724-6878</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Jl. Raden Sanim No.61, Tanah Baru, Kecamatan Beji, Kota Depok, Jawa Barat 16426, Indonesia</t>
+          <t>Jl. Kolonel Sugiono No.9B, RT.3/RW.6, Duren Sawit, Kec. Duren Sawit, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13430, Indonesia</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -4296,12 +4300,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>http://megabajadurensawit.com/</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=17885757876253202658&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=17718922127125026770&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4313,12 +4317,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Baja ringan depok</t>
+          <t>Spesial Besi Jakarta Barat - Distributor Besi, Baja dan Stainless Cengkareng</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0812-9931-2809</t>
+          <t>0899-0452-121</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4328,7 +4332,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Jl. Abdul Gani 1, Kalibaru, Kec. Cilodong, Kota Depok, Jawa Barat 16413, Indonesia</t>
+          <t>7, RT.7/RW.1, Rw. Buaya, Kecamatan Cengkareng, Kota Jakarta Barat, Daerah Khusus Ibukota Jakarta 11740, Indonesia</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -4341,7 +4345,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=3204311117804502232&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=5183172928918125425&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4353,12 +4357,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TATABAJA | Jasa Pasang Kanopi Baja Ringan | Area Jakarta, Depok, Bogor, Tangerang dan Bekasi</t>
+          <t>Mega Baja Bintaro</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0813-8182-8279</t>
+          <t>0821-2022-2656</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4368,20 +4372,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Jl. Swadaya Utama No.9A, Curug, Kec. Cimanggis, Kota Depok, Jawa Barat 16418, Indonesia</t>
+          <t>Jl. Cemp. V No.6 7, RT.6/RW.11, Bintaro, Kec. Pesanggrahan, Jakarta, Daerah Khusus Ibukota Jakarta 12330, Indonesia</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>http://www.tatabaja.com/</t>
+          <t>http://www.megabajabintaro.com/</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=1028867163558180687&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=12048754701944103310&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4393,12 +4397,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Langit Baja Mampang</t>
+          <t>Toko besi tunas baja bogor dan bahan bangunan</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0852-1832-1276</t>
+          <t>0822-222-633</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4408,7 +4412,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Jl. Pramuka Raya No.6, Mampang, Kec. Pancoran Mas, Kota Depok, Jawa Barat 16433, Indonesia</t>
+          <t>Jl. Re. Abdullah No.17, Pasir Jaya, Kec. Bogor Bar., Kota Bogor, Jawa Barat 16118, Indonesia</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4421,7 +4425,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=6031371296093665525&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=6328258046535728612&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4433,12 +4437,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Baja Ringan Depok</t>
+          <t>Mega Baja Condet</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0857-1969-2075</t>
+          <t>0822-1386-8474</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4448,7 +4452,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>HQH3+W3H, Pengasinan, Sawangan, Depok City, West Java 16518, Indonesia</t>
+          <t>Jl. Raya Condet No.16, RT.5/RW.3, Balekambang, Kec. Kramat jati, Kota Jakarta Timur, Daerah Khusus Ibukota Jakarta 13530, Indonesia</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -4456,12 +4460,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tidak ada website</t>
+          <t>https://megabajacondet.com/</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://maps.google.com/?cid=3328243586097992739&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+          <t>https://maps.google.com/?cid=6857354546375775890&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
